--- a/data/EquipAttributeCap.xlsx
+++ b/data/EquipAttributeCap.xlsx
@@ -480,8 +480,8 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -497,11 +497,11 @@
       <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="D7" t="n">
-        <v>90</v>
-      </c>
-      <c r="E7" t="n">
-        <v>300</v>
+      <c r="D7">
+        <v>75</v>
+      </c>
+      <c r="E7">
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -514,11 +514,11 @@
       <c r="C8" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="n">
-        <v>180</v>
-      </c>
-      <c r="E8" t="n">
-        <v>600</v>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -531,11 +531,11 @@
       <c r="C9" t="n">
         <v>60</v>
       </c>
-      <c r="D9" t="n">
-        <v>270</v>
-      </c>
-      <c r="E9" t="n">
-        <v>900</v>
+      <c r="D9">
+        <v>225</v>
+      </c>
+      <c r="E9">
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -548,11 +548,11 @@
       <c r="C10" t="n">
         <v>80</v>
       </c>
-      <c r="D10" t="n">
-        <v>360</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1200</v>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10">
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -565,11 +565,11 @@
       <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>30</v>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -582,11 +582,11 @@
       <c r="C12" t="n">
         <v>20</v>
       </c>
-      <c r="D12" t="n">
-        <v>120</v>
-      </c>
-      <c r="E12" t="n">
-        <v>400</v>
+      <c r="D12">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -599,11 +599,11 @@
       <c r="C13" t="n">
         <v>40</v>
       </c>
-      <c r="D13" t="n">
-        <v>240</v>
-      </c>
-      <c r="E13" t="n">
-        <v>800</v>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -616,11 +616,11 @@
       <c r="C14" t="n">
         <v>60</v>
       </c>
-      <c r="D14" t="n">
-        <v>360</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1200</v>
+      <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14">
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -633,11 +633,11 @@
       <c r="C15" t="n">
         <v>80</v>
       </c>
-      <c r="D15" t="n">
-        <v>480</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1600</v>
+      <c r="D15">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>400</v>
       </c>
     </row>
     <row r="16">
@@ -653,8 +653,8 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
+      <c r="E16">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -667,11 +667,11 @@
       <c r="C17" t="n">
         <v>20</v>
       </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -684,11 +684,11 @@
       <c r="C18" t="n">
         <v>40</v>
       </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>10</v>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -701,11 +701,11 @@
       <c r="C19" t="n">
         <v>60</v>
       </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15</v>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -718,11 +718,11 @@
       <c r="C20" t="n">
         <v>80</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
         <v>6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -738,8 +738,8 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
+      <c r="E21">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -752,11 +752,11 @@
       <c r="C22" t="n">
         <v>20</v>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -769,11 +769,11 @@
       <c r="C23" t="n">
         <v>40</v>
       </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10</v>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -786,11 +786,11 @@
       <c r="C24" t="n">
         <v>60</v>
       </c>
-      <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>15</v>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -803,11 +803,11 @@
       <c r="C25" t="n">
         <v>80</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
         <v>6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -823,8 +823,8 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
+      <c r="E26">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -837,11 +837,11 @@
       <c r="C27" t="n">
         <v>20</v>
       </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -854,11 +854,11 @@
       <c r="C28" t="n">
         <v>40</v>
       </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>10</v>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -871,11 +871,11 @@
       <c r="C29" t="n">
         <v>60</v>
       </c>
-      <c r="D29" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>15</v>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -888,11 +888,11 @@
       <c r="C30" t="n">
         <v>80</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
         <v>6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -908,8 +908,8 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
+      <c r="E31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -922,11 +922,11 @@
       <c r="C32" t="n">
         <v>20</v>
       </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5</v>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -939,11 +939,11 @@
       <c r="C33" t="n">
         <v>40</v>
       </c>
-      <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>10</v>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -956,11 +956,11 @@
       <c r="C34" t="n">
         <v>60</v>
       </c>
-      <c r="D34" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>15</v>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -973,11 +973,11 @@
       <c r="C35" t="n">
         <v>80</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
         <v>6</v>
-      </c>
-      <c r="E35" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1007,11 +1007,11 @@
       <c r="C37" t="n">
         <v>20</v>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4</v>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1024,11 +1024,11 @@
       <c r="C38" t="n">
         <v>40</v>
       </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="n">
-        <v>8</v>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1041,11 +1041,11 @@
       <c r="C39" t="n">
         <v>60</v>
       </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="n">
-        <v>12</v>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1058,11 +1058,11 @@
       <c r="C40" t="n">
         <v>80</v>
       </c>
-      <c r="D40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>16</v>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1075,11 +1075,11 @@
       <c r="C41" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>6</v>
+      <c r="D41">
+        <v>12</v>
+      </c>
+      <c r="E41">
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -1092,11 +1092,11 @@
       <c r="C42" t="n">
         <v>20</v>
       </c>
-      <c r="D42" t="n">
-        <v>24</v>
-      </c>
-      <c r="E42" t="n">
-        <v>80</v>
+      <c r="D42">
+        <v>90</v>
+      </c>
+      <c r="E42">
+        <v>180</v>
       </c>
     </row>
     <row r="43">
@@ -1109,11 +1109,11 @@
       <c r="C43" t="n">
         <v>40</v>
       </c>
-      <c r="D43" t="n">
-        <v>48</v>
-      </c>
-      <c r="E43" t="n">
-        <v>160</v>
+      <c r="D43">
+        <v>180</v>
+      </c>
+      <c r="E43">
+        <v>360</v>
       </c>
     </row>
     <row r="44">
@@ -1126,11 +1126,11 @@
       <c r="C44" t="n">
         <v>60</v>
       </c>
-      <c r="D44" t="n">
-        <v>72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>240</v>
+      <c r="D44">
+        <v>270</v>
+      </c>
+      <c r="E44">
+        <v>540</v>
       </c>
     </row>
     <row r="45">
@@ -1143,11 +1143,11 @@
       <c r="C45" t="n">
         <v>80</v>
       </c>
-      <c r="D45" t="n">
-        <v>96</v>
-      </c>
-      <c r="E45" t="n">
-        <v>320</v>
+      <c r="D45">
+        <v>360</v>
+      </c>
+      <c r="E45">
+        <v>720</v>
       </c>
     </row>
     <row r="46">
@@ -1160,11 +1160,11 @@
       <c r="C46" t="n">
         <v>1</v>
       </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>10</v>
+      <c r="D46">
+        <v>15</v>
+      </c>
+      <c r="E46">
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -1177,11 +1177,11 @@
       <c r="C47" t="n">
         <v>20</v>
       </c>
-      <c r="D47" t="n">
-        <v>48</v>
-      </c>
-      <c r="E47" t="n">
-        <v>160</v>
+      <c r="D47">
+        <v>120</v>
+      </c>
+      <c r="E47">
+        <v>240</v>
       </c>
     </row>
     <row r="48">
@@ -1194,11 +1194,11 @@
       <c r="C48" t="n">
         <v>40</v>
       </c>
-      <c r="D48" t="n">
-        <v>96</v>
-      </c>
-      <c r="E48" t="n">
-        <v>320</v>
+      <c r="D48">
+        <v>240</v>
+      </c>
+      <c r="E48">
+        <v>480</v>
       </c>
     </row>
     <row r="49">
@@ -1211,11 +1211,11 @@
       <c r="C49" t="n">
         <v>60</v>
       </c>
-      <c r="D49" t="n">
-        <v>144</v>
-      </c>
-      <c r="E49" t="n">
-        <v>480</v>
+      <c r="D49">
+        <v>360</v>
+      </c>
+      <c r="E49">
+        <v>720</v>
       </c>
     </row>
     <row r="50">
@@ -1228,11 +1228,11 @@
       <c r="C50" t="n">
         <v>80</v>
       </c>
-      <c r="D50" t="n">
-        <v>192</v>
-      </c>
-      <c r="E50" t="n">
-        <v>640</v>
+      <c r="D50">
+        <v>480</v>
+      </c>
+      <c r="E50">
+        <v>960</v>
       </c>
     </row>
     <row r="51">
@@ -1245,11 +1245,11 @@
       <c r="C51" t="n">
         <v>1</v>
       </c>
-      <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>8</v>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51">
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -1262,11 +1262,11 @@
       <c r="C52" t="n">
         <v>20</v>
       </c>
-      <c r="D52" t="n">
-        <v>36</v>
-      </c>
-      <c r="E52" t="n">
-        <v>120</v>
+      <c r="D52">
+        <v>80</v>
+      </c>
+      <c r="E52">
+        <v>160</v>
       </c>
     </row>
     <row r="53">
@@ -1279,11 +1279,11 @@
       <c r="C53" t="n">
         <v>40</v>
       </c>
-      <c r="D53" t="n">
-        <v>72</v>
-      </c>
-      <c r="E53" t="n">
-        <v>240</v>
+      <c r="D53">
+        <v>160</v>
+      </c>
+      <c r="E53">
+        <v>320</v>
       </c>
     </row>
     <row r="54">
@@ -1296,11 +1296,11 @@
       <c r="C54" t="n">
         <v>60</v>
       </c>
-      <c r="D54" t="n">
-        <v>108</v>
-      </c>
-      <c r="E54" t="n">
-        <v>360</v>
+      <c r="D54">
+        <v>240</v>
+      </c>
+      <c r="E54">
+        <v>480</v>
       </c>
     </row>
     <row r="55">
@@ -1313,11 +1313,11 @@
       <c r="C55" t="n">
         <v>80</v>
       </c>
-      <c r="D55" t="n">
-        <v>144</v>
-      </c>
-      <c r="E55" t="n">
-        <v>480</v>
+      <c r="D55">
+        <v>320</v>
+      </c>
+      <c r="E55">
+        <v>640</v>
       </c>
     </row>
     <row r="56">
@@ -1333,8 +1333,8 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="n">
-        <v>2</v>
+      <c r="E56">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1347,11 +1347,11 @@
       <c r="C57" t="n">
         <v>20</v>
       </c>
-      <c r="D57" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" t="n">
-        <v>4</v>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1367,8 +1367,8 @@
       <c r="D58" t="n">
         <v>2</v>
       </c>
-      <c r="E58" t="n">
-        <v>6</v>
+      <c r="E58">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1381,11 +1381,11 @@
       <c r="C59" t="n">
         <v>60</v>
       </c>
-      <c r="D59" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" t="n">
-        <v>8</v>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -1401,8 +1401,8 @@
       <c r="D60" t="n">
         <v>3</v>
       </c>
-      <c r="E60" t="n">
-        <v>10</v>
+      <c r="E60">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -1418,8 +1418,8 @@
       <c r="D61" t="n">
         <v>1</v>
       </c>
-      <c r="E61" t="n">
-        <v>2</v>
+      <c r="E61">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1432,11 +1432,11 @@
       <c r="C62" t="n">
         <v>20</v>
       </c>
-      <c r="D62" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4</v>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1452,8 +1452,8 @@
       <c r="D63" t="n">
         <v>2</v>
       </c>
-      <c r="E63" t="n">
-        <v>6</v>
+      <c r="E63">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -1466,11 +1466,11 @@
       <c r="C64" t="n">
         <v>60</v>
       </c>
-      <c r="D64" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" t="n">
-        <v>8</v>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -1486,8 +1486,8 @@
       <c r="D65" t="n">
         <v>3</v>
       </c>
-      <c r="E65" t="n">
-        <v>10</v>
+      <c r="E65">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -1503,8 +1503,8 @@
       <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
-        <v>2</v>
+      <c r="E66">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1517,11 +1517,11 @@
       <c r="C67" t="n">
         <v>20</v>
       </c>
-      <c r="D67" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" t="n">
-        <v>4</v>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1537,8 +1537,8 @@
       <c r="D68" t="n">
         <v>2</v>
       </c>
-      <c r="E68" t="n">
-        <v>6</v>
+      <c r="E68">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -1551,11 +1551,11 @@
       <c r="C69" t="n">
         <v>60</v>
       </c>
-      <c r="D69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>8</v>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -1571,8 +1571,8 @@
       <c r="D70" t="n">
         <v>3</v>
       </c>
-      <c r="E70" t="n">
-        <v>10</v>
+      <c r="E70">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -1588,8 +1588,8 @@
       <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="E71" t="n">
-        <v>2</v>
+      <c r="E71">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -1602,11 +1602,11 @@
       <c r="C72" t="n">
         <v>20</v>
       </c>
-      <c r="D72" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4</v>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -1622,8 +1622,8 @@
       <c r="D73" t="n">
         <v>2</v>
       </c>
-      <c r="E73" t="n">
-        <v>6</v>
+      <c r="E73">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -1636,11 +1636,11 @@
       <c r="C74" t="n">
         <v>60</v>
       </c>
-      <c r="D74" t="n">
-        <v>3</v>
-      </c>
-      <c r="E74" t="n">
-        <v>8</v>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -1656,8 +1656,8 @@
       <c r="D75" t="n">
         <v>3</v>
       </c>
-      <c r="E75" t="n">
-        <v>10</v>
+      <c r="E75">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -1673,8 +1673,8 @@
       <c r="D76" t="n">
         <v>1</v>
       </c>
-      <c r="E76" t="n">
-        <v>2</v>
+      <c r="E76">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1687,11 +1687,11 @@
       <c r="C77" t="n">
         <v>20</v>
       </c>
-      <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="n">
-        <v>4</v>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -1707,8 +1707,8 @@
       <c r="D78" t="n">
         <v>2</v>
       </c>
-      <c r="E78" t="n">
-        <v>6</v>
+      <c r="E78">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -1721,11 +1721,11 @@
       <c r="C79" t="n">
         <v>60</v>
       </c>
-      <c r="D79" t="n">
-        <v>3</v>
-      </c>
-      <c r="E79" t="n">
-        <v>8</v>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -1741,8 +1741,8 @@
       <c r="D80" t="n">
         <v>3</v>
       </c>
-      <c r="E80" t="n">
-        <v>10</v>
+      <c r="E80">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -1775,8 +1775,8 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="n">
-        <v>2</v>
+      <c r="E82">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -1792,8 +1792,8 @@
       <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E83" t="n">
-        <v>3</v>
+      <c r="E83">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -1806,11 +1806,11 @@
       <c r="C84" t="n">
         <v>60</v>
       </c>
-      <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" t="n">
-        <v>4</v>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -1823,11 +1823,11 @@
       <c r="C85" t="n">
         <v>80</v>
       </c>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>5</v>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
